--- a/financials/HPG/HPG_Q.xlsx
+++ b/financials/HPG/HPG_Q.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="12000" windowHeight="12900" tabRatio="600" firstSheet="4" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,6 @@
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hiệu quả thực hiện KH" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +30,7 @@
   </numFmts>
   <fonts count="20">
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -115,14 +111,14 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
@@ -152,7 +148,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
       <color rgb="FF7030A0"/>
@@ -282,7 +278,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -359,6 +355,12 @@
     <xf numFmtId="165" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,87 +579,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>22250</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="CĐKT"/>
-      <sheetName val="KQHĐKD"/>
-      <sheetName val="LCTT"/>
-      <sheetName val="Tổng quan"/>
-      <sheetName val="Dự báo tăng trưởng"/>
-      <sheetName val="Hiệu quả thực hiện KH của DN"/>
-      <sheetName val="Phân tích"/>
-      <sheetName val="Chart"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="4">
-          <cell r="O4">
-            <v>90119</v>
-          </cell>
-          <cell r="P4">
-            <v>149680</v>
-          </cell>
-          <cell r="Q4">
-            <v>141409</v>
-          </cell>
-          <cell r="R4">
-            <v>118953</v>
-          </cell>
-          <cell r="S4">
-            <v>138855</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="O21">
-            <v>13506</v>
-          </cell>
-          <cell r="P21">
-            <v>34521</v>
-          </cell>
-          <cell r="Q21">
-            <v>8444</v>
-          </cell>
-          <cell r="R21">
-            <v>6800</v>
-          </cell>
-          <cell r="S21">
-            <v>12020</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11530,11 +11451,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="38.33203125" customWidth="1" min="1" max="1"/>
-    <col width="17.44140625" customWidth="1" min="2" max="8"/>
-    <col width="21.88671875" bestFit="1" customWidth="1" min="9" max="10"/>
+    <col width="38.375" customWidth="1" min="1" max="1"/>
+    <col width="17.5" customWidth="1" min="2" max="8"/>
+    <col width="21.875" bestFit="1" customWidth="1" min="9" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -12911,7 +12832,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="1" s="43">
+    <row r="39" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu</t>
@@ -12954,7 +12875,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="1" s="49">
+    <row r="40" ht="15" customFormat="1" customHeight="1" s="49">
       <c r="A40" s="45" t="inlineStr">
         <is>
           <t>Tăng VCSH/LN cổ đông cty mẹ</t>
@@ -12991,7 +12912,7 @@
       </c>
       <c r="J40" s="58" t="n"/>
     </row>
-    <row r="41" customFormat="1" s="43">
+    <row r="41" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Lợi ích cổ đông không kiểm soát</t>
@@ -13038,7 +12959,7 @@
         </is>
       </c>
     </row>
-    <row r="43" customFormat="1" s="43">
+    <row r="43" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
@@ -13119,7 +13040,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="1" s="43">
+    <row r="45" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
@@ -13356,7 +13277,7 @@
         <v>22000000000000</v>
       </c>
     </row>
-    <row r="51" customFormat="1" s="43">
+    <row r="51" ht="15" customFormat="1" customHeight="1" s="43">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
@@ -14065,35 +13986,35 @@
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="62">
         <f>IFERROR(B$63/ABS(B$49),"n/a")</f>
         <v/>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="62">
         <f>IFERROR(C$63/ABS(C$49),"n/a")</f>
         <v/>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="62">
         <f>IFERROR(D$63/ABS(D$49),"n/a")</f>
         <v/>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="62">
         <f>IFERROR(E$63/ABS(E$49),"n/a")</f>
         <v/>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="62">
         <f>IFERROR(F$63/ABS(F$49),"n/a")</f>
         <v/>
       </c>
-      <c r="G74" s="16">
+      <c r="G74" s="62">
         <f>IFERROR(G$63/ABS(G$49),"n/a")</f>
         <v/>
       </c>
-      <c r="H74" s="16">
+      <c r="H74" s="62">
         <f>IFERROR(H$63/ABS(H$49),"n/a")</f>
         <v/>
       </c>
-      <c r="I74" s="16">
+      <c r="I74" s="62">
         <f>IFERROR(I$63/ABS(I$49),"n/a")</f>
         <v/>
       </c>
@@ -14290,35 +14211,35 @@
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="62">
         <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
         <v/>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="62">
         <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
         <v/>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="62">
         <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
         <v/>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="62">
         <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
         <v/>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="62">
         <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
         <v/>
       </c>
-      <c r="G81" s="16">
+      <c r="G81" s="62">
         <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
         <v/>
       </c>
-      <c r="H81" s="16">
+      <c r="H81" s="62">
         <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
         <v/>
       </c>
-      <c r="I81" s="16">
+      <c r="I81" s="62">
         <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
         <v/>
       </c>
@@ -14329,35 +14250,35 @@
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="62">
         <f>IFERROR(B$29/B$35,"n/a")</f>
         <v/>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="62">
         <f>IFERROR(C$29/C$35,"n/a")</f>
         <v/>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="62">
         <f>IFERROR(D$29/D$35,"n/a")</f>
         <v/>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="62">
         <f>IFERROR(E$29/E$35,"n/a")</f>
         <v/>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="62">
         <f>IFERROR(F$29/F$35,"n/a")</f>
         <v/>
       </c>
-      <c r="G82" s="16">
+      <c r="G82" s="62">
         <f>IFERROR(G$29/G$35,"n/a")</f>
         <v/>
       </c>
-      <c r="H82" s="16">
+      <c r="H82" s="62">
         <f>IFERROR(H$29/H$35,"n/a")</f>
         <v/>
       </c>
-      <c r="I82" s="16">
+      <c r="I82" s="62">
         <f>IFERROR(I$29/I$35,"n/a")</f>
         <v/>
       </c>
@@ -14527,14 +14448,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.21875" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="12.75"/>
   <cols>
-    <col width="8.21875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.25" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="32" min="2" max="5"/>
-    <col width="19.44140625" customWidth="1" style="32" min="6" max="8"/>
-    <col width="9.21875" bestFit="1" customWidth="1" style="32" min="9" max="10"/>
-    <col width="8.6640625" customWidth="1" style="32" min="11" max="17"/>
-    <col width="11.21875" customWidth="1" style="32" min="18" max="16384"/>
+    <col width="19.5" customWidth="1" style="32" min="6" max="8"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="32" min="9" max="10"/>
+    <col width="8.625" customWidth="1" style="32" min="11" max="17"/>
+    <col width="11.25" customWidth="1" style="32" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -14586,21 +14507,17 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="28">
-        <f>[1]Sheet1!$B$2</f>
-        <v/>
-      </c>
-      <c r="C3" s="28">
-        <f>[1]Sheet1!$B$2</f>
-        <v/>
-      </c>
-      <c r="D3" s="28">
-        <f>[1]Sheet1!$B$2</f>
-        <v/>
-      </c>
-      <c r="E3" s="28">
-        <f>[1]Sheet1!$B$2</f>
-        <v/>
+      <c r="B3" s="28" t="n">
+        <v>22250</v>
+      </c>
+      <c r="C3" s="28" t="n">
+        <v>22250</v>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>22250</v>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>22250</v>
       </c>
       <c r="F3" s="33" t="n"/>
     </row>
@@ -14635,22 +14552,22 @@
           <t>VCSH</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="63" t="n">
         <v>139782000000000</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="63" t="n">
         <v>141516000000000</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="63">
         <f>B6*(($E$6/$B$6)^(2/3))</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="63">
         <f>chi_so_tai_chinh!J39</f>
         <v/>
       </c>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="35" t="n"/>
+      <c r="F6" s="64" t="n"/>
+      <c r="G6" s="65" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
@@ -14683,19 +14600,19 @@
           <t>BV</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="63">
         <f>B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="63">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="63">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="63">
         <f>E6-E7</f>
         <v/>
       </c>
@@ -14709,19 +14626,19 @@
           <t>BVPS</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="66">
         <f>B8/B2</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="66">
         <f>C8/C2</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="66">
         <f>D8/D2</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="66">
         <f>E8/E2</f>
         <v/>
       </c>
@@ -14732,19 +14649,19 @@
           <t>PB</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="67">
         <f>$E$3/B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="67">
         <f>$E$3/C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="67">
         <f>$E$3/D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="67">
         <f>$E$3/E9</f>
         <v/>
       </c>
@@ -14795,13 +14712,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.21875" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="12.75"/>
   <cols>
-    <col width="40.33203125" customWidth="1" style="32" min="1" max="1"/>
-    <col width="10.109375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="7"/>
-    <col width="8.6640625" customWidth="1" style="32" min="8" max="21"/>
-    <col width="11.21875" customWidth="1" style="32" min="22" max="16384"/>
+    <col width="40.375" customWidth="1" style="32" min="1" max="1"/>
+    <col width="10.125" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="32" min="3" max="7"/>
+    <col width="8.625" customWidth="1" style="32" min="8" max="21"/>
+    <col width="11.25" customWidth="1" style="32" min="22" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14861,23 +14778,23 @@
         </is>
       </c>
       <c r="B3" s="28">
-        <f>[2]KQHĐKD!O4*1000</f>
+        <f>chi_so_tai_chinh!D43/1000000</f>
         <v/>
       </c>
       <c r="C3" s="28">
-        <f>[2]KQHĐKD!P4*1000</f>
+        <f>chi_so_tai_chinh!E43/1000000</f>
         <v/>
       </c>
       <c r="D3" s="28">
-        <f>[2]KQHĐKD!Q4*1000</f>
+        <f>chi_so_tai_chinh!F43/1000000</f>
         <v/>
       </c>
       <c r="E3" s="28">
-        <f>[2]KQHĐKD!R4*1000</f>
+        <f>chi_so_tai_chinh!G43/1000000</f>
         <v/>
       </c>
       <c r="F3" s="28">
-        <f>[2]KQHĐKD!S4*1000</f>
+        <f>chi_so_tai_chinh!H43/1000000</f>
         <v/>
       </c>
       <c r="G3" s="28" t="n"/>
@@ -14942,23 +14859,23 @@
         </is>
       </c>
       <c r="B6" s="28">
-        <f>[2]KQHĐKD!O21*1000</f>
+        <f>chi_so_tai_chinh!D50/1000000</f>
         <v/>
       </c>
       <c r="C6" s="28">
-        <f>[2]KQHĐKD!P21*1000</f>
+        <f>chi_so_tai_chinh!E50/1000000</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>[2]KQHĐKD!Q21*1000</f>
+        <f>chi_so_tai_chinh!F50/1000000</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>[2]KQHĐKD!R21*1000</f>
+        <f>chi_so_tai_chinh!G50/1000000</f>
         <v/>
       </c>
       <c r="F6" s="28">
-        <f>[2]KQHĐKD!S21*1000</f>
+        <f>chi_so_tai_chinh!H50/1000000</f>
         <v/>
       </c>
       <c r="G6" s="28" t="n"/>
